--- a/public/exports/29189846.xlsx
+++ b/public/exports/29189846.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279891</t>
+          <t xml:space="preserve">311279903</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279890</t>
+          <t xml:space="preserve">311279903</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311282669</t>
+          <t xml:space="preserve">311372348</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -19339,12 +19339,12 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369509</t>
+          <t xml:space="preserve">311374076</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -21964,12 +21964,12 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290661</t>
+          <t xml:space="preserve">311290663</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290666</t>
+          <t xml:space="preserve">311374773</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -23989,12 +23989,12 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291095</t>
+          <t xml:space="preserve">311373742</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M320" t="inlineStr">
@@ -24439,12 +24439,12 @@
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293774</t>
+          <t xml:space="preserve">311373757</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M326" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293846</t>
+          <t xml:space="preserve">311293847</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">

--- a/public/exports/29189846.xlsx
+++ b/public/exports/29189846.xlsx
@@ -6889,12 +6889,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279903</t>
+          <t xml:space="preserve">311279891</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7039,12 +7039,12 @@
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t xml:space="preserve">311279903</t>
+          <t xml:space="preserve">311279890</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372348</t>
+          <t xml:space="preserve">311282669</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -19339,12 +19339,12 @@
       </c>
       <c r="K258" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374076</t>
+          <t xml:space="preserve">311369509</t>
         </is>
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
@@ -21964,12 +21964,12 @@
       </c>
       <c r="K293" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290663</t>
+          <t xml:space="preserve">311290661</t>
         </is>
       </c>
       <c r="L293" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M293" t="inlineStr">
@@ -22039,7 +22039,7 @@
       </c>
       <c r="K294" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374773</t>
+          <t xml:space="preserve">311290666</t>
         </is>
       </c>
       <c r="L294" t="inlineStr">
@@ -22091,7 +22091,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stænderpladsen 2</t>
+          <t xml:space="preserve">Tapdrupvej 100</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
@@ -22101,20 +22101,20 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">9431029</t>
+          <t xml:space="preserve">3454867</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J295">
-        <v>1500</v>
+        <v>488</v>
       </c>
       <c r="K295" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368829</t>
+          <t xml:space="preserve">311375102</t>
         </is>
       </c>
       <c r="L295" t="inlineStr">
@@ -22181,15 +22181,15 @@
       </c>
       <c r="I296" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J296">
-        <v>488</v>
+        <v>284</v>
       </c>
       <c r="K296" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375102</t>
+          <t xml:space="preserve">311375108</t>
         </is>
       </c>
       <c r="L296" t="inlineStr">
@@ -22241,7 +22241,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tapdrupvej 100</t>
+          <t xml:space="preserve">Tapdrupvej 100A</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
@@ -22256,15 +22256,15 @@
       </c>
       <c r="I297" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J297">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="K297" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375108</t>
+          <t xml:space="preserve">311368613</t>
         </is>
       </c>
       <c r="L297" t="inlineStr">
@@ -22316,7 +22316,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tapdrupvej 100A</t>
+          <t xml:space="preserve">Tingvej 17</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
@@ -22326,20 +22326,20 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">3454867</t>
+          <t xml:space="preserve">5589413</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">30</t>
         </is>
       </c>
       <c r="J298">
-        <v>273</v>
+        <v>1281</v>
       </c>
       <c r="K298" t="inlineStr">
         <is>
-          <t xml:space="preserve">311368613</t>
+          <t xml:space="preserve">311375539</t>
         </is>
       </c>
       <c r="L298" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 17</t>
+          <t xml:space="preserve">Tingvej 5</t>
         </is>
       </c>
       <c r="G299" t="inlineStr">
@@ -22401,20 +22401,20 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589413</t>
+          <t xml:space="preserve">5591355</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
         <is>
-          <t xml:space="preserve">30</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J299">
-        <v>1281</v>
+        <v>3916</v>
       </c>
       <c r="K299" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375539</t>
+          <t xml:space="preserve">311375512</t>
         </is>
       </c>
       <c r="L299" t="inlineStr">
@@ -22466,7 +22466,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 5</t>
+          <t xml:space="preserve">Vinkelvej 172</t>
         </is>
       </c>
       <c r="G300" t="inlineStr">
@@ -22476,20 +22476,20 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591355</t>
+          <t xml:space="preserve">4012634</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J300">
-        <v>3916</v>
+        <v>387</v>
       </c>
       <c r="K300" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375512</t>
+          <t xml:space="preserve">311375598</t>
         </is>
       </c>
       <c r="L300" t="inlineStr">
@@ -22541,7 +22541,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 172</t>
+          <t xml:space="preserve">Vinkelvej 18A</t>
         </is>
       </c>
       <c r="G301" t="inlineStr">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t xml:space="preserve">4012634</t>
+          <t xml:space="preserve">8838279</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -22560,11 +22560,11 @@
         </is>
       </c>
       <c r="J301">
-        <v>387</v>
+        <v>284</v>
       </c>
       <c r="K301" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375598</t>
+          <t xml:space="preserve">311290692</t>
         </is>
       </c>
       <c r="L301" t="inlineStr">
@@ -22616,17 +22616,17 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vinkelvej 18A</t>
+          <t xml:space="preserve">Vorningvej 33</t>
         </is>
       </c>
       <c r="G302" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8830</t>
         </is>
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">8838279</t>
+          <t xml:space="preserve">3468562</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -22635,11 +22635,11 @@
         </is>
       </c>
       <c r="J302">
-        <v>284</v>
+        <v>5165</v>
       </c>
       <c r="K302" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290692</t>
+          <t xml:space="preserve">311375628</t>
         </is>
       </c>
       <c r="L302" t="inlineStr">
@@ -22691,7 +22691,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorningvej 33</t>
+          <t xml:space="preserve">Vorningvej 33A</t>
         </is>
       </c>
       <c r="G303" t="inlineStr">
@@ -22706,15 +22706,15 @@
       </c>
       <c r="I303" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J303">
-        <v>5165</v>
+        <v>813</v>
       </c>
       <c r="K303" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375628</t>
+          <t xml:space="preserve">311290695</t>
         </is>
       </c>
       <c r="L303" t="inlineStr">
@@ -22766,30 +22766,30 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vorningvej 33A</t>
+          <t xml:space="preserve">Ådalshøjen 2</t>
         </is>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t xml:space="preserve">8830</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t xml:space="preserve">3468562</t>
+          <t xml:space="preserve">8074164</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J304">
-        <v>813</v>
+        <v>722</v>
       </c>
       <c r="K304" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290695</t>
+          <t xml:space="preserve">311375648</t>
         </is>
       </c>
       <c r="L304" t="inlineStr">
@@ -22841,17 +22841,17 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ådalshøjen 2</t>
+          <t xml:space="preserve">Skolen 3</t>
         </is>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7470</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t xml:space="preserve">8074164</t>
+          <t xml:space="preserve">9214926</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -22860,11 +22860,11 @@
         </is>
       </c>
       <c r="J305">
-        <v>722</v>
+        <v>2661</v>
       </c>
       <c r="K305" t="inlineStr">
         <is>
-          <t xml:space="preserve">311375648</t>
+          <t xml:space="preserve">311372723</t>
         </is>
       </c>
       <c r="L305" t="inlineStr">
@@ -22874,7 +22874,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-28</t>
+          <t xml:space="preserve">2027-12-29</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -22931,11 +22931,11 @@
       </c>
       <c r="I306" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J306">
-        <v>2661</v>
+        <v>1945</v>
       </c>
       <c r="K306" t="inlineStr">
         <is>
@@ -23006,11 +23006,11 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J307">
-        <v>1945</v>
+        <v>422</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -23081,11 +23081,11 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J308">
-        <v>422</v>
+        <v>1025</v>
       </c>
       <c r="K308" t="inlineStr">
         <is>
@@ -23156,11 +23156,11 @@
       </c>
       <c r="I309" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J309">
-        <v>1025</v>
+        <v>898</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -23216,30 +23216,30 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolen 3</t>
+          <t xml:space="preserve">Egeskovvej 75</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t xml:space="preserve">7470</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">9214926</t>
+          <t xml:space="preserve">3451289</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J310">
-        <v>898</v>
+        <v>1067</v>
       </c>
       <c r="K310" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372723</t>
+          <t xml:space="preserve">311290810</t>
         </is>
       </c>
       <c r="L310" t="inlineStr">
@@ -23249,7 +23249,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-29</t>
+          <t xml:space="preserve">2027-12-30</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -23306,11 +23306,11 @@
       </c>
       <c r="I311" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J311">
-        <v>1067</v>
+        <v>444</v>
       </c>
       <c r="K311" t="inlineStr">
         <is>
@@ -23381,11 +23381,11 @@
       </c>
       <c r="I312" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J312">
-        <v>444</v>
+        <v>976</v>
       </c>
       <c r="K312" t="inlineStr">
         <is>
@@ -23456,11 +23456,11 @@
       </c>
       <c r="I313" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J313">
-        <v>976</v>
+        <v>1673</v>
       </c>
       <c r="K313" t="inlineStr">
         <is>
@@ -23531,11 +23531,11 @@
       </c>
       <c r="I314" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J314">
-        <v>1673</v>
+        <v>3803</v>
       </c>
       <c r="K314" t="inlineStr">
         <is>
@@ -23606,11 +23606,11 @@
       </c>
       <c r="I315" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J315">
-        <v>3803</v>
+        <v>380</v>
       </c>
       <c r="K315" t="inlineStr">
         <is>
@@ -23681,15 +23681,15 @@
       </c>
       <c r="I316" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J316">
-        <v>380</v>
+        <v>306</v>
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290810</t>
+          <t xml:space="preserve">311290811</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23741,7 +23741,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskovvej 75</t>
+          <t xml:space="preserve">Egeskovvej 4</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
@@ -23751,20 +23751,20 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">3451289</t>
+          <t xml:space="preserve">8371196</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">57</t>
         </is>
       </c>
       <c r="J317">
-        <v>306</v>
+        <v>275</v>
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311290811</t>
+          <t xml:space="preserve">311291090</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t xml:space="preserve">2027-12-30</t>
+          <t xml:space="preserve">2028-01-04</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -23816,35 +23816,35 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egeskovvej 4</t>
+          <t xml:space="preserve">Gl. Banevej 8</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7470</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">8371196</t>
+          <t xml:space="preserve">379840, 379841</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
         <is>
-          <t xml:space="preserve">57</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J318">
-        <v>275</v>
+        <v>3301</v>
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291090</t>
+          <t xml:space="preserve">311291149</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M318" t="inlineStr">
@@ -23891,17 +23891,17 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Banevej 8</t>
+          <t xml:space="preserve">Kærsangervej 252</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t xml:space="preserve">7470</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">379840, 379841</t>
+          <t xml:space="preserve">7715426</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -23910,11 +23910,11 @@
         </is>
       </c>
       <c r="J319">
-        <v>3301</v>
+        <v>635</v>
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291149</t>
+          <t xml:space="preserve">311291095</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -23966,7 +23966,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kærsangervej 252</t>
+          <t xml:space="preserve">Safranvej 10A</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
@@ -23976,20 +23976,20 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t xml:space="preserve">7715426</t>
+          <t xml:space="preserve">9254134</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J320">
-        <v>635</v>
+        <v>267</v>
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373742</t>
+          <t xml:space="preserve">311291091</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -24041,7 +24041,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Safranvej 10A</t>
+          <t xml:space="preserve">Sct. Laurentii Vej 14C</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
@@ -24051,25 +24051,25 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">9254134</t>
+          <t xml:space="preserve">5591308</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J321">
-        <v>267</v>
+        <v>384</v>
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291091</t>
+          <t xml:space="preserve">311372532</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M321" t="inlineStr">
@@ -24116,35 +24116,35 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct. Laurentii Vej 14C</t>
+          <t xml:space="preserve">Tjele Møllevej 10</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8830</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">5591308</t>
+          <t xml:space="preserve">3455227</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J322">
-        <v>384</v>
+        <v>2628</v>
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372532</t>
+          <t xml:space="preserve">311291101</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M322" t="inlineStr">
@@ -24191,17 +24191,17 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tjele Møllevej 10</t>
+          <t xml:space="preserve">Guldblommevej 14</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t xml:space="preserve">8830</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">3455227</t>
+          <t xml:space="preserve">5587531</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -24210,11 +24210,11 @@
         </is>
       </c>
       <c r="J323">
-        <v>2628</v>
+        <v>836</v>
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311291101</t>
+          <t xml:space="preserve">311293801</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -24224,7 +24224,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-04</t>
+          <t xml:space="preserve">2028-01-22</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -24266,7 +24266,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldblommevej 14</t>
+          <t xml:space="preserve">Guldblommevej 16</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
@@ -24281,7 +24281,7 @@
       </c>
       <c r="I324" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J324">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293801</t>
+          <t xml:space="preserve">311293850</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -24341,7 +24341,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldblommevej 16</t>
+          <t xml:space="preserve">Liseborg Hegn 10A</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
@@ -24351,25 +24351,25 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t xml:space="preserve">5587531</t>
+          <t xml:space="preserve">10227103</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J325">
-        <v>836</v>
+        <v>6616</v>
       </c>
       <c r="K325" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293850</t>
+          <t xml:space="preserve">311293774</t>
         </is>
       </c>
       <c r="L325" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M325" t="inlineStr">
@@ -24416,7 +24416,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liseborg Hegn 10A</t>
+          <t xml:space="preserve">Ll. Sct. Hans Gade 7</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
@@ -24426,20 +24426,20 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t xml:space="preserve">10227103</t>
+          <t xml:space="preserve">100002554</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J326">
-        <v>6616</v>
+        <v>464</v>
       </c>
       <c r="K326" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373757</t>
+          <t xml:space="preserve">311373762</t>
         </is>
       </c>
       <c r="L326" t="inlineStr">
@@ -24491,7 +24491,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ll. Sct. Hans Gade 7</t>
+          <t xml:space="preserve">Ll. Sct. Hans Gade 9</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
@@ -24506,11 +24506,11 @@
       </c>
       <c r="I327" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J327">
-        <v>464</v>
+        <v>1037</v>
       </c>
       <c r="K327" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ll. Sct. Hans Gade 9</t>
+          <t xml:space="preserve">Merkurvej 71</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
@@ -24576,7 +24576,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t xml:space="preserve">100002554</t>
+          <t xml:space="preserve">3449917</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -24585,11 +24585,11 @@
         </is>
       </c>
       <c r="J328">
-        <v>1037</v>
+        <v>594</v>
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373762</t>
+          <t xml:space="preserve">311293846</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24641,7 +24641,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t xml:space="preserve">Merkurvej 71</t>
+          <t xml:space="preserve">Rødevej 2A</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -24651,7 +24651,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t xml:space="preserve">3449917</t>
+          <t xml:space="preserve">8940099</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -24660,11 +24660,11 @@
         </is>
       </c>
       <c r="J329">
-        <v>594</v>
+        <v>1569</v>
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293847</t>
+          <t xml:space="preserve">311374142</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -24716,17 +24716,17 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rødevej 2A</t>
+          <t xml:space="preserve">Skolegade 27</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">9632</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940099</t>
+          <t xml:space="preserve">3464052</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -24735,11 +24735,11 @@
         </is>
       </c>
       <c r="J330">
-        <v>1569</v>
+        <v>2918</v>
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374142</t>
+          <t xml:space="preserve">311372613</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
@@ -24806,15 +24806,15 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J331">
-        <v>2918</v>
+        <v>294</v>
       </c>
       <c r="K331" t="inlineStr">
         <is>
-          <t xml:space="preserve">311372613</t>
+          <t xml:space="preserve">311374196</t>
         </is>
       </c>
       <c r="L331" t="inlineStr">
@@ -24881,15 +24881,15 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J332">
-        <v>294</v>
+        <v>2275</v>
       </c>
       <c r="K332" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374196</t>
+          <t xml:space="preserve">311293831</t>
         </is>
       </c>
       <c r="L332" t="inlineStr">
@@ -24956,15 +24956,15 @@
       </c>
       <c r="I333" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J333">
-        <v>2275</v>
+        <v>333</v>
       </c>
       <c r="K333" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293831</t>
+          <t xml:space="preserve">311293833</t>
         </is>
       </c>
       <c r="L333" t="inlineStr">
@@ -25016,7 +25016,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 27</t>
+          <t xml:space="preserve">Skolegade 29</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
@@ -25031,15 +25031,15 @@
       </c>
       <c r="I334" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J334">
-        <v>333</v>
+        <v>297</v>
       </c>
       <c r="K334" t="inlineStr">
         <is>
-          <t xml:space="preserve">311293833</t>
+          <t xml:space="preserve">311374191</t>
         </is>
       </c>
       <c r="L334" t="inlineStr">
@@ -25091,40 +25091,40 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolegade 29</t>
+          <t xml:space="preserve">Liseborgvej 35A</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t xml:space="preserve">9632</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464052</t>
+          <t xml:space="preserve">1508276, 100535682</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">12</t>
         </is>
       </c>
       <c r="J335">
-        <v>297</v>
+        <v>854</v>
       </c>
       <c r="K335" t="inlineStr">
         <is>
-          <t xml:space="preserve">311374191</t>
+          <t xml:space="preserve">311373759</t>
         </is>
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-01-22</t>
+          <t xml:space="preserve">2028-02-15</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -25166,40 +25166,40 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t xml:space="preserve">Liseborgvej 35A</t>
+          <t xml:space="preserve">Brandstrupvej 27</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8840</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t xml:space="preserve">1508276, 100535682</t>
+          <t xml:space="preserve">4011561</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
         <is>
-          <t xml:space="preserve">12</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J336">
-        <v>854</v>
+        <v>1178</v>
       </c>
       <c r="K336" t="inlineStr">
         <is>
-          <t xml:space="preserve">311373759</t>
+          <t xml:space="preserve">311369993</t>
         </is>
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Dansk Energisyn</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t xml:space="preserve">2028-02-15</t>
+          <t xml:space="preserve">2029-04-09</t>
         </is>
       </c>
       <c r="N336" t="inlineStr">
@@ -25241,40 +25241,40 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brandstrupvej 27</t>
+          <t xml:space="preserve">Stadionvej 6A</t>
         </is>
       </c>
       <c r="G337" t="inlineStr">
         <is>
-          <t xml:space="preserve">8840</t>
+          <t xml:space="preserve">8832</t>
         </is>
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t xml:space="preserve">4011561</t>
+          <t xml:space="preserve">3464853</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J337">
-        <v>1178</v>
+        <v>335</v>
       </c>
       <c r="K337" t="inlineStr">
         <is>
-          <t xml:space="preserve">311369993</t>
+          <t xml:space="preserve">311467972</t>
         </is>
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Energisyn</t>
+          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-04-09</t>
+          <t xml:space="preserve">2030-10-19</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -25316,40 +25316,40 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stadionvej 6A</t>
+          <t xml:space="preserve">Rørsangervej 5</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t xml:space="preserve">8832</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">3464853</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J338">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="K338" t="inlineStr">
         <is>
-          <t xml:space="preserve">311467972</t>
+          <t xml:space="preserve">311476458</t>
         </is>
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dansk Bygningsrådgivning ApS</t>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-10-19</t>
+          <t xml:space="preserve">2030-11-17</t>
         </is>
       </c>
       <c r="N338" t="inlineStr">
@@ -25391,7 +25391,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørsangervej 5</t>
+          <t xml:space="preserve">Søakset 2</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
@@ -25401,30 +25401,30 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">100124844</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J339">
-        <v>313</v>
+        <v>1565</v>
       </c>
       <c r="K339" t="inlineStr">
         <is>
-          <t xml:space="preserve">311476458</t>
+          <t xml:space="preserve">311505527</t>
         </is>
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-11-17</t>
+          <t xml:space="preserve">2031-03-22</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -25466,40 +25466,40 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søakset 2</t>
+          <t xml:space="preserve">Naundrupvej 7A</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">9632</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t xml:space="preserve">100124844</t>
+          <t xml:space="preserve">749066, 3456742</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J340">
-        <v>1565</v>
+        <v>348</v>
       </c>
       <c r="K340" t="inlineStr">
         <is>
-          <t xml:space="preserve">311505527</t>
+          <t xml:space="preserve">311540479</t>
         </is>
       </c>
       <c r="L340" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-03-22</t>
+          <t xml:space="preserve">2031-08-12</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -25541,40 +25541,40 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Naundrupvej 7A</t>
+          <t xml:space="preserve">Anlægsgade 2</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t xml:space="preserve">9632</t>
+          <t xml:space="preserve">7850</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">749066, 3456742</t>
+          <t xml:space="preserve">384187, 384188</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J341">
-        <v>348</v>
+        <v>3245</v>
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311540479</t>
+          <t xml:space="preserve">311619862</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
         </is>
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-08-12</t>
+          <t xml:space="preserve">2032-08-11</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -25616,17 +25616,17 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Anlægsgade 2</t>
+          <t xml:space="preserve">Tingvej 20</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t xml:space="preserve">7850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t xml:space="preserve">384187, 384188</t>
+          <t xml:space="preserve">5589417</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -25635,21 +25635,21 @@
         </is>
       </c>
       <c r="J342">
-        <v>3245</v>
+        <v>8141</v>
       </c>
       <c r="K342" t="inlineStr">
         <is>
-          <t xml:space="preserve">311619862</t>
+          <t xml:space="preserve">311652390</t>
         </is>
       </c>
       <c r="L342" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+          <t xml:space="preserve">Norconsult A/S</t>
         </is>
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-11</t>
+          <t xml:space="preserve">2033-01-04</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -25691,7 +25691,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tingvej 20</t>
+          <t xml:space="preserve">H.C. Andersens Vej 5</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
@@ -25701,30 +25701,30 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">5589417</t>
+          <t xml:space="preserve">5590613</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">15</t>
         </is>
       </c>
       <c r="J343">
-        <v>8141</v>
+        <v>478</v>
       </c>
       <c r="K343" t="inlineStr">
         <is>
-          <t xml:space="preserve">311652390</t>
+          <t xml:space="preserve">311659256</t>
         </is>
       </c>
       <c r="L343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norconsult A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-04</t>
+          <t xml:space="preserve">2033-02-09</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -25766,7 +25766,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t xml:space="preserve">H.C. Andersens Vej 5</t>
+          <t xml:space="preserve">Rørsangervej 5</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
@@ -25776,30 +25776,30 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590613</t>
+          <t xml:space="preserve">5586340</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J344">
-        <v>478</v>
+        <v>357</v>
       </c>
       <c r="K344" t="inlineStr">
         <is>
-          <t xml:space="preserve">311659256</t>
+          <t xml:space="preserve">311661783</t>
         </is>
       </c>
       <c r="L344" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-09</t>
+          <t xml:space="preserve">2033-02-22</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -25841,7 +25841,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rørsangervej 5</t>
+          <t xml:space="preserve">Banegårdspladsen 4</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
@@ -25851,30 +25851,30 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">5586340</t>
+          <t xml:space="preserve">381021, 381022, 381023, 381024, 381025</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J345">
-        <v>357</v>
+        <v>1814</v>
       </c>
       <c r="K345" t="inlineStr">
         <is>
-          <t xml:space="preserve">311661783</t>
+          <t xml:space="preserve">311702960</t>
         </is>
       </c>
       <c r="L345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
         </is>
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-02-22</t>
+          <t xml:space="preserve">2033-08-27</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -25916,40 +25916,40 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Banegårdspladsen 4</t>
+          <t xml:space="preserve">Jørgens Alle 42</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">8850</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t xml:space="preserve">381021, 381022, 381023, 381024, 381025</t>
+          <t xml:space="preserve">7775696</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J346">
-        <v>1814</v>
+        <v>394</v>
       </c>
       <c r="K346" t="inlineStr">
         <is>
-          <t xml:space="preserve">311702960</t>
+          <t xml:space="preserve">311764588</t>
         </is>
       </c>
       <c r="L346" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
         </is>
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-27</t>
+          <t xml:space="preserve">2034-06-06</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -25991,40 +25991,40 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jørgens Alle 42</t>
+          <t xml:space="preserve">Gl. Randersvej 35</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t xml:space="preserve">8850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">7775696</t>
+          <t xml:space="preserve">8837678</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J347">
-        <v>394</v>
+        <v>13000</v>
       </c>
       <c r="K347" t="inlineStr">
         <is>
-          <t xml:space="preserve">311764588</t>
+          <t xml:space="preserve">311797218</t>
         </is>
       </c>
       <c r="L347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ydes Bygningsrådgivning</t>
+          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
         </is>
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-06-06</t>
+          <t xml:space="preserve">2034-11-13</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -26066,7 +26066,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gl. Randersvej 35</t>
+          <t xml:space="preserve">Rughavevej 66</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
@@ -26076,30 +26076,30 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">8837678</t>
+          <t xml:space="preserve">5590174</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">18</t>
         </is>
       </c>
       <c r="J348">
-        <v>13000</v>
+        <v>683</v>
       </c>
       <c r="K348" t="inlineStr">
         <is>
-          <t xml:space="preserve">311797218</t>
+          <t xml:space="preserve">311805525</t>
         </is>
       </c>
       <c r="L348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Trykprøvning &amp; Energimærkning Danmark ApS</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-11-13</t>
+          <t xml:space="preserve">2035-01-13</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -26141,7 +26141,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rughavevej 66</t>
+          <t xml:space="preserve">Sct. Leonis Gade 8</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
@@ -26151,30 +26151,30 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t xml:space="preserve">5590174</t>
+          <t xml:space="preserve">5585392</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t xml:space="preserve">18</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J349">
-        <v>683</v>
+        <v>310</v>
       </c>
       <c r="K349" t="inlineStr">
         <is>
-          <t xml:space="preserve">311805525</t>
+          <t xml:space="preserve">311858724</t>
         </is>
       </c>
       <c r="L349" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Norconsult Danmark A/S</t>
         </is>
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-01-13</t>
+          <t xml:space="preserve">2035-09-29</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -26216,17 +26216,17 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sct. Leonis Gade 8</t>
+          <t xml:space="preserve">Iglsøvej 68B</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t xml:space="preserve">8800</t>
+          <t xml:space="preserve">7850</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t xml:space="preserve">5585392</t>
+          <t xml:space="preserve">4048544</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -26235,21 +26235,21 @@
         </is>
       </c>
       <c r="J350">
-        <v>310</v>
+        <v>515</v>
       </c>
       <c r="K350" t="inlineStr">
         <is>
-          <t xml:space="preserve">311858724</t>
+          <t xml:space="preserve">311869171</t>
         </is>
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t xml:space="preserve">Norconsult Danmark A/S</t>
+          <t xml:space="preserve">Tæthedskompagniet ApS</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-29</t>
+          <t xml:space="preserve">2035-11-19</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -26291,40 +26291,40 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Iglsøvej 68B</t>
+          <t xml:space="preserve">Martinesminde 2</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t xml:space="preserve">7850</t>
+          <t xml:space="preserve">8800</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">4048544</t>
+          <t xml:space="preserve">100617942</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J351">
-        <v>515</v>
+        <v>349</v>
       </c>
       <c r="K351" t="inlineStr">
         <is>
-          <t xml:space="preserve">311869171</t>
+          <t xml:space="preserve">311881722</t>
         </is>
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tæthedskompagniet ApS</t>
+          <t xml:space="preserve">Sweco Danmark A/S</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-19</t>
+          <t xml:space="preserve">2036-02-12</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -26366,7 +26366,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martinesminde 2</t>
+          <t xml:space="preserve">Stænderpladsen 2</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
@@ -26376,30 +26376,30 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t xml:space="preserve">100617942</t>
+          <t xml:space="preserve">9431029</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J352">
-        <v>349</v>
+        <v>1500</v>
       </c>
       <c r="K352" t="inlineStr">
         <is>
-          <t xml:space="preserve">311881722</t>
+          <t xml:space="preserve">311929568</t>
         </is>
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-02-12</t>
+          <t xml:space="preserve">2036-10-02</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
